--- a/AAII_Financials/Quarterly/SWKS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/SWKS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>SWKS</t>
   </si>
@@ -656,540 +656,552 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="26" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="27" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E7" s="2">
         <v>46115</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46024</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45933</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44925</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44743</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44652</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44470</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44379</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44288</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44197</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44106</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44008</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43917</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43826</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43735</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43644</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43553</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43462</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43371</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43189</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43098</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43007</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42734</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>934800</v>
+      </c>
+      <c r="E8" s="3">
         <v>943700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1035400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1100200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>965000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>953200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1068500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1025000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>905500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1046000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1201500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1218800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1071200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1153100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1329300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1406900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1232600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1335600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1510400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1310900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1116400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1171800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1510000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>956800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>736800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>766100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>896100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>827400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>767000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>810400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>972000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1008400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>894300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>913400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1051900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>984600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>900800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>851700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>914300</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>835400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>559800</v>
+      </c>
+      <c r="E9" s="3">
         <v>558400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>608200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>652700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>564000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>561600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>626600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>595200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>541400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>625700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>694900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>740700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>607100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>625700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>691600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>738300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>649300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>698000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>795700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>697200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>557800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>593400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>748300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>497900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>402700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>390500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>451800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>421400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>454500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>410200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>486900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>504800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>442700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>454700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>515100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>485700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>447200</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>426300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>450400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>411000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>375000</v>
+      </c>
+      <c r="E10" s="3">
         <v>385300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>427200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>447500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>401000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>391600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>441900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>429800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>364100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>420300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>506600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>478100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>464100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>527400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>637700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>668600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>583300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>637600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>714700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>613700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>558600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>578400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>761700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>458900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>334100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>375600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>444300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>406000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>312500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>400200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>485100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>503600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>451600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>458700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>536800</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>498900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>453600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>425400</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>463900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>424400</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,130 +1244,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>207800</v>
+      </c>
+      <c r="E12" s="3">
         <v>212400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>203400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>223100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>199400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>186500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>176400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>163600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>160700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>154400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>153100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>146800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>148000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>148200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>163900</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>149500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>156500</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>160700</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>151100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>149200</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>130800</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>130700</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>121600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>126200</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>117000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>113200</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>107700</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>106800</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>100600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>107500</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>109200</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>103000</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>96800</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>106700</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>98000</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>91800</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>92000</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>89400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>82000</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>73200</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,74 +1492,77 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E14" s="3">
         <v>30600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>48500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>132500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>16200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>21400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>4700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>500</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
@@ -1551,55 +1570,58 @@
         <v>0</v>
       </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>11800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>1200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>5500</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>1500</v>
-      </c>
-      <c r="AG14" s="3">
-        <v>-200</v>
       </c>
       <c r="AH14" s="3">
         <v>-200</v>
       </c>
       <c r="AI14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
         <v>1000</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="3">
         <v>-200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>200</v>
       </c>
-      <c r="AN14" s="3">
-        <v>0</v>
-      </c>
       <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
         <v>600</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1634,16 +1656,16 @@
         <v>200</v>
       </c>
       <c r="N15" s="3">
+        <v>200</v>
+      </c>
+      <c r="O15" s="3">
         <v>3700</v>
-      </c>
-      <c r="O15" s="3">
-        <v>3800</v>
       </c>
       <c r="P15" s="3">
         <v>3800</v>
       </c>
       <c r="Q15" s="3">
-        <v>21900</v>
+        <v>3800</v>
       </c>
       <c r="R15" s="3">
         <v>21900</v>
@@ -1655,16 +1677,16 @@
         <v>21900</v>
       </c>
       <c r="U15" s="3">
+        <v>21900</v>
+      </c>
+      <c r="V15" s="3">
         <v>33300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>28100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>2400</v>
-      </c>
-      <c r="X15" s="3">
-        <v>2800</v>
       </c>
       <c r="Y15" s="3">
         <v>2800</v>
@@ -1676,52 +1698,55 @@
         <v>2800</v>
       </c>
       <c r="AB15" s="3">
-        <v>3100</v>
+        <v>2800</v>
       </c>
       <c r="AC15" s="3">
         <v>3100</v>
       </c>
       <c r="AD15" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AE15" s="3">
         <v>4000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>5500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>5700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>7400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>6300</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>4100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>4000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>5000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>7100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>7000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>8500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>6400</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1786,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>852300</v>
+      </c>
+      <c r="E17" s="3">
         <v>871000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>883100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>987600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>852900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>848800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>885800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>833100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>773500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>857100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>927000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>964500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>836100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>856700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>962300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1018800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>906800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>968300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1064500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>983400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>776600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>797100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>939300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>689200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>589300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>566600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>618800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>593500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>607400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>572800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>651100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>668300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>588000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>624000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>668400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>638700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>596000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>570500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>592400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>543500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>82500</v>
+      </c>
+      <c r="E18" s="3">
         <v>72700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>152300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>112600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>112100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>104400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>182700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>191900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>132000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>188900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>274500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>254300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>235100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>296400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>367000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>388100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>325800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>367300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>445900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>327500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>339800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>374700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>570700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>267600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>147500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>199500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>277300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>233900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>159600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>237600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>320900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>340100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>306300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>289400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>383500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>345900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>304800</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>281200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>321900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>291900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,317 +2081,324 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-10800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-12200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-11900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-16100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-5900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-7600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>1800</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>200</v>
-      </c>
-      <c r="AO20" s="3">
-        <v>-800</v>
       </c>
       <c r="AP20" s="3">
         <v>-800</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>-800</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>88900</v>
+      </c>
+      <c r="E21" s="3">
         <v>83700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>164700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>130700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>120300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>116500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>199000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>198000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>141800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>199900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>278100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>262600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>246500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>305600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>539000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>567900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>488200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>529900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>628600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>497100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>429800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>464800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>657300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>356800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>234600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>294800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>369900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>326900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>255600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>333300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>416800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>427200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>385500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>363900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>454700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>413100</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>369500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>344300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>384900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>352300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E22" s="3">
         <v>7500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>6800</v>
       </c>
       <c r="I22" s="3">
         <v>6800</v>
       </c>
       <c r="J22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>10000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>10900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>2600</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>24</v>
@@ -2376,8 +2415,8 @@
       <c r="AC22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -2415,252 +2454,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E23" s="3">
         <v>45400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>109700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>122000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>112000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>102400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>190400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>133400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>192900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>251700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>246200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>222100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>259800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>350700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>372200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>314100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>354100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>436100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>316200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>336200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>375500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>570900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>266100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>144000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>203000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>278700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>234000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>161900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>241300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>323800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>343400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>310800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>292300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>385600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>347700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>306800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>281400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>321100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>291100</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E24" s="3">
         <v>9800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-19400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>33700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>12500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>20400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>41300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>70000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>46800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>48300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>36200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-10100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>50500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>61600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>19000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>14300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>21900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>21600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>15300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>17800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>27300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>38900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>71500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>33200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>38900</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>66400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>60600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>56500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>63300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>44300</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2829,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E26" s="3">
         <v>35600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>79200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>141400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>105000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>68700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>162000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>60500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>120900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>183300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>231300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>244800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>195800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>232800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>309400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>302200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>267300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>305800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>399900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>326300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>337800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>325000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>509300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>247100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>129700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>181100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>257100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>218700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>144100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>214000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>284900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>271900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>283600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>259100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>346700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>281300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>246200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>224900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>257800</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>246800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E27" s="3">
         <v>35600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>79200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>141400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>105000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>68700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>162000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>60500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>120900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>183300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>231300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>244800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>195800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>232800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>309400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>302200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>267300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>305800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>399900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>326300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>337800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>325000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>509300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>247100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>129700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>181100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>257100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>218700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>144100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>214000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>284900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>271900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>283600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>259100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>346700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>281300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>246200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>224900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>257800</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>246800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3204,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3200,17 +3260,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>24</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>24</v>
@@ -3218,11 +3278,11 @@
       <c r="Y29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>24</v>
@@ -3230,11 +3290,11 @@
       <c r="AC29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-8100</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>24</v>
@@ -3242,20 +3302,20 @@
       <c r="AG29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AI29" s="3">
         <v>13600</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>16900</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-276300</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3269,8 +3329,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3454,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,252 +3579,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E32" s="3">
         <v>10800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>12200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>11900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>16100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>5900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>7600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-1800</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-200</v>
-      </c>
-      <c r="AO32" s="3">
-        <v>800</v>
       </c>
       <c r="AP32" s="3">
         <v>800</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>800</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E33" s="3">
         <v>35600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>79200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>141400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>105000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>68700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>162000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>60500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>120900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>183300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>231300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>244800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>195800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>232800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>309400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>302200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>267300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>305800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>399900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>326300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>337800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>325000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>509300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>246900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>129700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>181100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>257100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>210600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>144100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>214000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>284900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>285500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>286500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>276000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>70400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>281300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>246200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>224900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>257800</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>246800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3954,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E35" s="3">
         <v>35600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>79200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>141400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>105000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>68700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>162000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>60500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>120900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>183300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>231300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>244800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>195800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>232800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>309400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>302200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>267300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>305800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>399900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>326300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>337800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>325000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>509300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>246900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>129700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>181100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>257100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>210600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>144100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>214000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>284900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>285500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>286500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>276000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>70400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>281300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>246200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>224900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>257800</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>246800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E38" s="2">
         <v>46115</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46024</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45933</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44925</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44743</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44652</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44470</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44379</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44288</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44197</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44106</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44008</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43917</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43826</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43735</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43644</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43553</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43462</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43371</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43189</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43098</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43007</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42734</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4256,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,231 +4301,235 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>790000</v>
+      </c>
+      <c r="E41" s="3">
         <v>1413300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1550400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1161300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1185900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1387800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1602500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1368600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1263400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1205400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1029700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>718800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>721600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>832600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>819900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>566000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>643000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>656400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>876400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>882900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2845000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1059900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>617200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>566700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>791300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>912400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>928200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>851300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>742800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>816300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1085700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>733300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1158100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1881300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1681500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1616800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1444000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1406900</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1350500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1083800</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>9200</v>
+      </c>
+      <c r="E42" s="3">
         <v>8500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>8300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>212900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>132000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>118800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>136700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>194100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>12900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>14900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>228800</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>172700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>20300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>16200</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>118400</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>137000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>137200</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>129200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>359700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>401400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>408100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>347000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>161500</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>262200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>203300</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>192200</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>141100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>13400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>294100</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>384400</v>
-      </c>
-      <c r="AJ42" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>24</v>
@@ -4460,496 +4549,511 @@
       <c r="AP42" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ42" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>348200</v>
+      </c>
+      <c r="E43" s="3">
         <v>336000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>398400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>598100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>396200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>371900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>520000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>508800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>607400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>615300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>659400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>864300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>726800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>685000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>764100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1094000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>785600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>798100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>774000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>756200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>570500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>499000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>689900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>393600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>346100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>367600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>426800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>465300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>557800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>543800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>524400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>655800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>468400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>367200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>458800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>454700</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>397400</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>368800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>368400</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>416600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1015500</v>
+      </c>
+      <c r="E44" s="3">
         <v>885600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>767500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>754700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>706500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>678300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>699700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>784800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>822800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>835500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>926800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1119700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1235600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1257000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1273300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1212100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1102000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>928200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>838500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>885000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>808700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>739800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>718500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>806000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>698200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>648900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>604400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>609700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>580800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>555000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>493100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>490200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>502800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>466400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>458600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>493500</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>482500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>444500</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>422800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>424000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>305300</v>
+      </c>
+      <c r="E45" s="3">
         <v>247800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>167900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>149000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>257400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>264200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>261800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>249900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>306200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>215000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>166400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>155100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>131000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>127000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>384300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>337500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>361200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>274400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>237500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>204100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>168500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>146300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>148200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>143200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>154800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>130400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>124900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>105000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>132700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>103900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>91900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>88800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>117700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>96000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>87700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>68700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>88100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>87900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>56800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>77700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2710900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3125600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3103000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3077000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2876400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3035500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3443800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3341000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3239100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3145500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3086600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3179500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3124900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3399200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3414300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3229900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>2908000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2775500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2863400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2865400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4521900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2804700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2575200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2317600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>2337400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>2220800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>2346500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>2234600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2206300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2160100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>2208500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>2262200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2631400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>2810900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>2686600</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>2633700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>2412000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2308100</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>2198500</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>2002100</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4957,100 +5061,100 @@
         <v>14600</v>
       </c>
       <c r="E47" s="3">
+        <v>14600</v>
+      </c>
+      <c r="F47" s="3">
         <v>9900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>18800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>15600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>14900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3000</v>
       </c>
-      <c r="P47" s="3" t="s">
+      <c r="Q47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
         <v>500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>24100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>34100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>38200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>27600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>35100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>33900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>22800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>106300</v>
-      </c>
-      <c r="AJ47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AK47" s="3" t="s">
         <v>24</v>
@@ -5070,252 +5174,261 @@
       <c r="AP47" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ47" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1380400</v>
+      </c>
+      <c r="E48" s="3">
         <v>1370000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1363700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1387000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1409900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1432100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1435300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1471900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1462300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1506300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1546900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1595500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1631200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1707100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1777500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1827800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1815700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1786300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1734100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1667700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1614800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1564600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1477800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1417400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1379600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1379200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1349900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1205600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1230100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1169800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1140600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1140900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1034600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>907100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>869100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>882300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>857700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>800400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>801500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>806300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2855500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2898300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2941200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2985700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3028900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3015500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3060700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3077200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3252300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3296200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3339100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3398800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3446300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3498300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3549700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3621400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3718500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3742500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3808300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3875300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1224500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1228900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1236200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1243300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1252700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1275200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1286300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1297700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1303900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1319700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1319900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1333500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>942900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>945700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>951200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>950800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>942600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>949700</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>955300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>940300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5549,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,130 +5674,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E52" s="3">
         <v>101600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>74500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>77500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>77200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>78000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>72200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>78300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>74900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>164800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>60900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>56500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>120400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>118200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>205900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>194200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>249400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>203900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>209200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>175200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>121100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>132200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>129900</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>123200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>78600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>72600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>70900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>74100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>66900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>82000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>67200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>69500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>68100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>81400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>87400</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>106800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>97900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>108600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>110400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>106700</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5924,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>7425000</v>
+      </c>
+      <c r="E54" s="3">
         <v>7896000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7867900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7917000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7714600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7885700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8331100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8283300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8236400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8309700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8229100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8426700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8464100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8841700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8947400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8873800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>8694600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>8511600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>8618500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>8590700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>7486200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5734400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5419800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5106700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5072400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4981900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5091800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4839600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4842300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4765500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4738900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4828900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4783300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4745100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4594300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4573600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4310200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4166800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>4065700</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>3855400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6096,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,183 +6141,187 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>268600</v>
+      </c>
+      <c r="E57" s="3">
         <v>266200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>209300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>236000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>205500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>193100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>147200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>171800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>160900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>149800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>135700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>159200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>160100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>165800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>180300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>274200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>319900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>296300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>279400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>236000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>319500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>276200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>264600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>226900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>200900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>169500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>138500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>190500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>218900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>167900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>156500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>229900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>230200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>198400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>161600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>258400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>178700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>163800</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>161500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>110400</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E58" s="3">
         <v>536400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>538000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>536200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>535200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>24300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>19300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>20200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>19700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>327700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>177800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>528400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>499500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>499200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>498800</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>24</v>
@@ -6205,8 +6338,8 @@
       <c r="Y58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Z58" s="3">
-        <v>0</v>
+      <c r="Z58" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AA58" s="3">
         <v>0</v>
@@ -6256,318 +6389,327 @@
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E59" s="3">
         <v>374900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>419200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>370300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>317700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>285500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>315300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>282800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>266400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>329900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>357200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>374500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>390900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>371000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>545700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>453500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>407400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>400300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>402500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>422500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>258800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>262200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>243000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>221500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>200200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>192700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>194700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>183500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>177600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>170400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>200800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>159800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>128100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>120100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>159900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>129500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>122100</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>103100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>141900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>99800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>874300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1315700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1295000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1323200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1205000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>613200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>579600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>602700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>562900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>606400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>615100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>955700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>816900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1168700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1225500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1226900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1226100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>696600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>681900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>658500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>578300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>538400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>507600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>448400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>401100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>362200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>333200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>374000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>396500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>338300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>357300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>389700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>358300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>318500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>321500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>387900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>300800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>266900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>303400</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>210200</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>644800</v>
+      </c>
+      <c r="E61" s="3">
         <v>653200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>654900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>666900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>672600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1185300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1173700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1180200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1181100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1189800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1184600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1181600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1534500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1690600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1690300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1689900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1689400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2187300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2186500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2235600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1487100</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -6622,130 +6764,136 @@
       <c r="AP61" s="3">
         <v>0</v>
       </c>
+      <c r="AQ61" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>167600</v>
+      </c>
+      <c r="E62" s="3">
         <v>161400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>159100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>169800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>184500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>146900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>177100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>163700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>156000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>154300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>202200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>206700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>234800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>249500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>481700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>488000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>484500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>439100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>415900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>399500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>418000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>483700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>497300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>494100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>488900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>476900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>491300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>343300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>345900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>346300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>343300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>342200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>342100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>356400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>372300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>120000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>111600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>108100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>102000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>103800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7014,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7139,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7264,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1686700</v>
+      </c>
+      <c r="E66" s="3">
         <v>2130300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2109000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2159900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2062100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1945400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1930400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1946600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1900000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1950500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2001900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2344000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2586200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3108800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3397500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3404800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3400000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3323000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3284300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3293600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2483400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1022100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1004900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>942500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>890000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>839100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>824500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>717300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>742400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>684600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>700600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>731900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>700400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>674900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>693800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>507900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>412400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>375000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>405400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>314000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7436,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7559,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7684,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7809,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7934,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5485500</v>
+      </c>
+      <c r="E72" s="3">
         <v>5558500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>5629700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>5656900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>5621100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5907600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6082400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6032900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6084400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6072600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5998400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5876000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5739700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5642600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5511900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5421900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5885100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5707800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5493200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5185800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4952100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>5489100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>5246700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4820400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4657000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4600800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4494600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4312600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4177100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4098700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>3950700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>3732900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>3515400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>3286800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>3069300</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3059600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>2837200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>2642600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>2469500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2263600</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8184,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8309,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8434,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5738300</v>
+      </c>
+      <c r="E76" s="3">
         <v>5765700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5758900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5757100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5652500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5940300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6400700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6336700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6336400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6359200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6227200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6082700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5877900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5732900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5549900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5469000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5294600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5188600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5334200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5297100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5002800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4712300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4414900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4164200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4182400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4142800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4267300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4122300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4099900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4080900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4038300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4097000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4082900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4070200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3900500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4065700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3897800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3791800</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3660300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3541400</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8684,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46206</v>
+      </c>
+      <c r="E80" s="2">
         <v>46115</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46024</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45933</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44925</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44743</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44652</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44470</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44379</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44288</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44197</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44106</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44008</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43917</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43826</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43735</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43644</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43553</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43462</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43371</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43280</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43189</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43098</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43007</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42734</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>33900</v>
+      </c>
+      <c r="E81" s="3">
         <v>35600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>79200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>141400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>105000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>68700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>162000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>60500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>120900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>183300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>231300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>244800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>195800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>232800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>309400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>302200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>267300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>305800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>399900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>326300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>337800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>325000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>509300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>246900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>129700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>181100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>257100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>210600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>144100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>214000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>284900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>285500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>286500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>276000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>70400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>281300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>246200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>224900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>257800</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>246800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,130 +8986,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>70100</v>
+      </c>
+      <c r="E83" s="3">
         <v>68600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>67600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>68500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>66300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>65300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>64700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>92000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>97400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>99000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>99400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-8100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>97000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>98400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>171400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>181400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>162800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>164400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>181500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>170000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>91000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>89300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>86400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>90700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>90600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>91800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>91200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>92900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>93700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>92000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>93000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>83800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>74700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>71600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>69100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>65400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>62700</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>62900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>63800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>61200</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9234,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9359,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9484,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9609,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9734,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>70400</v>
+      </c>
+      <c r="E89" s="3">
         <v>50300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>395500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>200000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>314200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>409400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>377200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>476100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>273400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>300300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>774900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>365500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>305800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>411700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>773400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>236300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>213800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>392800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>581700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>398300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>272900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>615700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>485100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>267000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>258700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>280400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>398400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>417000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>209300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>192100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>549000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>207600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>258000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>434200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>360800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>425400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>314100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>235900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>495900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>455000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9906,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-87100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-82400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-61500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-38500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-39000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-82800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-24400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-27600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-22200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-70100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-31300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-71300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-145700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-127500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-134900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-101600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-269900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-115000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-140900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-118900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-145900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-71600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-111200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-84400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-87800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-96700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-129500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-112300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-191500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-90300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-85300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-113000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-159900</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-50100</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-21200</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10154,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10279,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-85200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-92200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>139000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-131100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-32900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>7500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-271400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-28000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-78200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>183000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-106100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-223100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-147300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-17200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-116400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-98000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3032200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>113900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-103900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-111000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-190400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-254500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>44000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-180500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-101800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-138500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-268100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>171500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-341200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-684700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-90300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-34200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-97400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-113000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-54900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-60600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-21800</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,130 +10451,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E96" s="3">
         <v>106800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>106400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>105600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>103900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>110600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>112500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>112000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>109100</v>
       </c>
       <c r="L96" s="3">
         <v>109100</v>
       </c>
       <c r="M96" s="3">
+        <v>109100</v>
+      </c>
+      <c r="N96" s="3">
         <v>108900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>108500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>98700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>98600</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-99400</v>
       </c>
       <c r="R96" s="3">
         <v>-99400</v>
       </c>
       <c r="S96" s="3">
+        <v>-99400</v>
+      </c>
+      <c r="T96" s="3">
         <v>-90000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-91200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-92500</v>
       </c>
       <c r="V96" s="3">
         <v>-92500</v>
       </c>
       <c r="W96" s="3">
+        <v>-92500</v>
+      </c>
+      <c r="X96" s="3">
         <v>-82500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-82600</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-83000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-83500</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-73500</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-74900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-75100</v>
       </c>
       <c r="AD96" s="3">
         <v>-75100</v>
       </c>
       <c r="AE96" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-65700</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-66000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-67100</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-68000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-57700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-58400</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-59100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-58900</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-51600</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-51900</v>
-      </c>
-      <c r="AO96" s="3">
-        <v>-52200</v>
       </c>
       <c r="AP96" s="3">
         <v>-52200</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>-52200</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10699,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10824,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,130 +10949,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-608500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-95200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-145400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-93500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-438600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-591200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-150800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-99500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-187400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-91600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-440500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-290100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-599800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-292900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-296400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-166000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-210000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-496400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-490200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>671800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1398300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-69100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-323600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-301200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-125300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-340200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-206700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-144300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-193400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-368100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-291200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-296500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-144100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-261900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-155200</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-171200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-117400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-168600</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-323100</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10873,8 +11121,8 @@
       <c r="P101" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10951,126 +11199,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-623300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-137100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>389100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-24600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-201900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-214700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>233900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>105200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>58000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>175700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>310900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-111000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>12700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>253900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-77000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-220000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1962100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1785100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>442700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>50500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-224600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-121100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-15800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>76900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>108500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-73500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-269400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>352400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-424800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-723200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>199800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>64700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>172800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>37100</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>56400</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>266700</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>110100</v>
       </c>
     </row>
